--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.56953014823937</v>
+        <v>6.755048649088897</v>
       </c>
       <c r="D2" t="n">
-        <v>40.16578872663528</v>
+        <v>6.526940668078234</v>
       </c>
       <c r="E2" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F2" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.29048649034566</v>
+        <v>8.172204054681169</v>
       </c>
       <c r="D3" t="n">
-        <v>47.07045305679296</v>
+        <v>7.648948621728857</v>
       </c>
       <c r="E3" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F3" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.42499328785894</v>
+        <v>9.331561409277079</v>
       </c>
       <c r="D4" t="n">
-        <v>54.09867158066722</v>
+        <v>8.791034131858424</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F4" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.54640152420322</v>
+        <v>4.151290247683024</v>
       </c>
       <c r="D5" t="n">
-        <v>26.45124888498198</v>
+        <v>4.298327943809571</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F5" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.94927722386648</v>
+        <v>3.404257548878303</v>
       </c>
       <c r="D6" t="n">
-        <v>17.80095118731091</v>
+        <v>2.892654567938023</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F6" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.99574526241125</v>
+        <v>9.911808605141829</v>
       </c>
       <c r="D7" t="n">
-        <v>10.22260820699743</v>
+        <v>1.661173833637083</v>
       </c>
       <c r="E7" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F7" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.94984695636319</v>
+        <v>9.416850130409019</v>
       </c>
       <c r="D8" t="n">
-        <v>14.44045805119355</v>
+        <v>2.346574433318951</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F8" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.99117359102765</v>
+        <v>7.473565708541994</v>
       </c>
       <c r="D9" t="n">
-        <v>44.40432347772371</v>
+        <v>7.215702565130103</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F9" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.75191687476156</v>
+        <v>9.059686492148755</v>
       </c>
       <c r="D10" t="n">
-        <v>31.34559672427572</v>
+        <v>5.093659467694805</v>
       </c>
       <c r="E10" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F10" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.21711147437242</v>
+        <v>8.972780614585519</v>
       </c>
       <c r="D11" t="n">
-        <v>57.06653767754257</v>
+        <v>9.273312372600667</v>
       </c>
       <c r="E11" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F11" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>66.15883287178421</v>
+        <v>10.75081034166494</v>
       </c>
       <c r="D12" t="n">
-        <v>68.68381612845141</v>
+        <v>11.16112012087335</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F12" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.50931446587327</v>
+        <v>10.64526360070441</v>
       </c>
       <c r="D13" t="n">
-        <v>67.75423350505308</v>
+        <v>11.01006294457113</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9325745141625</v>
+        <v>2.264043358551407</v>
       </c>
       <c r="F13" t="n">
-        <v>19.24348983963128</v>
+        <v>3.127067098940083</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
